--- a/backtest_runs/20260410_193731/by_symbol/KOSM/KOSM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/KOSM/KOSM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-1754.400000000001</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>104386</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>104386</v>
@@ -909,7 +909,7 @@
         <v>-3289.500000000008</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>118859.8</v>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>118859.8</v>
@@ -1047,7 +1047,7 @@
         <v>-2631.600000000002</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>121491.4</v>
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>121491.4</v>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>121491.4</v>
@@ -1231,7 +1231,7 @@
         <v>-1535.100000000006</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>119956.3</v>
@@ -1277,7 +1277,7 @@
         <v>-4166.699999999989</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>115789.6</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>116228.2</v>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>116228.2</v>
